--- a/practice/answers/s1_q25.xlsx
+++ b/practice/answers/s1_q25.xlsx
@@ -583,14 +583,14 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Larch</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
-        <v>41.2</v>
+        <v>39.7</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>120</v>
+        <v>145</v>
       </c>
       <c r="D9" s="4">
         <f>(B9*$B$4-$B$5)*C9*(1-$B$6)</f>
@@ -608,14 +608,14 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>South</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>38.6</v>
+        <v>43.1</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>240</v>
+        <v>268</v>
       </c>
       <c r="D10" s="4">
         <f>(B10*$B$4-$B$5)*C10*(1-$B$6)</f>
@@ -633,14 +633,14 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Creek</t>
+          <t>Nordegg</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>44.8</v>
+        <v>47.5</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="D11" s="4">
         <f>(B11*$B$4-$B$5)*C11*(1-$B$6)</f>
@@ -686,7 +686,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>-$18,539.96 for North. Without the brackets Excel subtracts the input cost for the whole field from the revenue of a single acre. Anything that must be netted before it is scaled has to be bracketed.</t>
+          <t>-$22,545.63 for Larch. Without the brackets Excel subtracts the input cost for the whole field from the revenue of a single acre. Anything that must be netted before it is scaled has to be bracketed.</t>
         </is>
       </c>
     </row>

--- a/practice/answers/s1_q25.xlsx
+++ b/practice/answers/s1_q25.xlsx
@@ -583,7 +583,7 @@
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Larch</t>
+          <t>Oxbow</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
@@ -608,7 +608,7 @@
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Prairie Rose</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
@@ -633,7 +633,7 @@
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Nordegg</t>
+          <t>Quill</t>
         </is>
       </c>
       <c r="B11" s="9" t="n">
@@ -686,7 +686,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>-$22,545.63 for Larch. Without the brackets Excel subtracts the input cost for the whole field from the revenue of a single acre. Anything that must be netted before it is scaled has to be bracketed.</t>
+          <t>-$22,545.63 for Oxbow. Without the brackets Excel subtracts the input cost for the whole field from the revenue of a single acre. Anything that must be netted before it is scaled has to be bracketed.</t>
         </is>
       </c>
     </row>

--- a/practice/answers/s1_q25.xlsx
+++ b/practice/answers/s1_q25.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,45 +29,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -76,12 +41,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -97,35 +77,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -491,210 +465,251 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Where the brackets go</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Revenue and cost are both per acre, so they have to be netted before the result is scaled by acres. Multiplication happens first unless you say otherwise.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Acres</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Net to farmer</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Price ($/bu)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="F1" s="3" t="n">
         <v>14.2</v>
       </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Input cost ($/ac)</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Net per acre</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Oxbow</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="D2" s="3">
+        <f>(B2*$F$1-$F$2)*C2*(1-$F$3)</f>
+        <v/>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Cost ($/ac)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>212.5</v>
       </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="H2" s="7">
+        <f>(B2*$F$1-$F$2)*(1-$F$3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Prairie Rose</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>268</v>
+      </c>
+      <c r="D3" s="3">
+        <f>(B3*$F$1-$F$2)*C3*(1-$F$3)</f>
+        <v/>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Landlord share</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="F3" s="8" t="n">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="7" ht="18" customHeight="1"/>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>Acres</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Net to farmer</t>
-        </is>
-      </c>
-      <c r="E8" s="7" t="inlineStr">
-        <is>
-          <t>Net per acre</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>The formula in D</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Oxbow</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n">
-        <v>39.7</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>145</v>
-      </c>
-      <c r="D9" s="4">
-        <f>(B9*$B$4-$B$5)*C9*(1-$B$6)</f>
+      <c r="H3" s="7">
+        <f>(B3*$F$1-$F$2)*(1-$F$3)</f>
         <v/>
       </c>
-      <c r="E9" s="4">
-        <f>(B9*$B$4-$B$5)*(1-$B$6)</f>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Quill</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="D4" s="3">
+        <f>(B4*$F$1-$F$2)*C4*(1-$F$3)</f>
         <v/>
       </c>
-      <c r="F9" s="11">
-        <f>_xlfn.FORMULATEXT(D9)</f>
+      <c r="H4" s="7">
+        <f>(B4*$F$1-$F$2)*(1-$F$3)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>Prairie Rose</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="n">
-        <v>43.1</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>268</v>
-      </c>
-      <c r="D10" s="4">
-        <f>(B10*$B$4-$B$5)*C10*(1-$B$6)</f>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D5" s="10">
+        <f>SUM(D2:D4)</f>
         <v/>
       </c>
-      <c r="E10" s="4">
-        <f>(B10*$B$4-$B$5)*(1-$B$6)</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
-        <f>_xlfn.FORMULATEXT(D10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Quill</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>112</v>
-      </c>
-      <c r="D11" s="4">
-        <f>(B11*$B$4-$B$5)*C11*(1-$B$6)</f>
-        <v/>
-      </c>
-      <c r="E11" s="4">
-        <f>(B11*$B$4-$B$5)*(1-$B$6)</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
-        <f>_xlfn.FORMULATEXT(D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="D12" s="12">
-        <f>SUM(D9:D11)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1"/>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>The formula without brackets</t>
-        </is>
-      </c>
-      <c r="D14" s="4">
-        <f>B9*$B$4-$B$5*C9*(1-$B$6)</f>
-        <v/>
-      </c>
-      <c r="F14" s="11">
-        <f>_xlfn.FORMULATEXT(D14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1"/>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>-$22,545.63 for Oxbow. Without the brackets Excel subtracts the input cost for the whole field from the revenue of a single acre. Anything that must be netted before it is scaled has to be bracketed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Without brackets Excel multiplies before it subtracts, so their formula takes the per-acre revenue and subtracts the whole-field input cost with the farmer's share already applied -- 212.50 x acres x 0.75 -- giving -$22,545.64 for Oxbow. Revenue and cost must be netted per acre first: =(B2*$F$1-$F$2)*C2*(1-$F$3).</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n"/>
+      <c r="C7" s="12" t="n"/>
+      <c r="D7" s="12" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="12" t="n"/>
+      <c r="G7" s="12" t="n"/>
+      <c r="H7" s="12" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="n"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="n"/>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Subtraction happens after multiplication unless brackets say otherwise, so anything that must be netted before it is scaled has to be bracketed.</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
+      <c r="G12" s="14" t="n"/>
+      <c r="H12" s="14" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n"/>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+      <c r="D13" s="14" t="n"/>
+      <c r="E13" s="14" t="n"/>
+      <c r="F13" s="14" t="n"/>
+      <c r="G13" s="14" t="n"/>
+      <c r="H13" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A7:H10"/>
+    <mergeCell ref="A12:H13"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
